--- a/Trazabilidad_WM-LMT2026_14_08_2026.xlsx
+++ b/Trazabilidad_WM-LMT2026_14_08_2026.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01675FB1-157F-434D-B1A6-957F8D8CB7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0EA0BF-9015-4DA8-BD32-CF7214148BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progreso_WM-LMT2026" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Progreso_WM-LMT2026'!$A$1:$T$86</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,9 +42,6 @@
     <t>longitud_poste</t>
   </si>
   <si>
-    <t>cantidad_aisladores</t>
-  </si>
-  <si>
     <t>metros_tendido</t>
   </si>
   <si>
@@ -391,6 +391,9 @@
   </si>
   <si>
     <t>11/08/2026</t>
+  </si>
+  <si>
+    <t>cantidad aisladores</t>
   </si>
 </sst>
 </file>
@@ -783,66 +786,66 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -857,45 +860,45 @@
         <v>11.11</v>
       </c>
       <c r="K2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -910,45 +913,45 @@
         <v>11.11</v>
       </c>
       <c r="K3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -963,45 +966,45 @@
         <v>11.11</v>
       </c>
       <c r="K4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -1016,45 +1019,45 @@
         <v>11.11</v>
       </c>
       <c r="K5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1069,45 +1072,45 @@
         <v>11.11</v>
       </c>
       <c r="K6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -1122,45 +1125,45 @@
         <v>11.11</v>
       </c>
       <c r="K7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -1175,45 +1178,45 @@
         <v>11.11</v>
       </c>
       <c r="K8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -1228,45 +1231,45 @@
         <v>11.11</v>
       </c>
       <c r="K9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1281,45 +1284,45 @@
         <v>11.11</v>
       </c>
       <c r="K10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1334,45 +1337,45 @@
         <v>11.11</v>
       </c>
       <c r="K11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -1387,45 +1390,45 @@
         <v>11.11</v>
       </c>
       <c r="K12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1440,45 +1443,45 @@
         <v>11.11</v>
       </c>
       <c r="K13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1493,45 +1496,45 @@
         <v>11.11</v>
       </c>
       <c r="K14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -1546,45 +1549,45 @@
         <v>11.11</v>
       </c>
       <c r="K15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1599,45 +1602,45 @@
         <v>11.11</v>
       </c>
       <c r="K16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1652,45 +1655,45 @@
         <v>11.11</v>
       </c>
       <c r="K17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -1705,45 +1708,45 @@
         <v>11.11</v>
       </c>
       <c r="K18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1758,45 +1761,45 @@
         <v>11.11</v>
       </c>
       <c r="K19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1811,45 +1814,45 @@
         <v>11.11</v>
       </c>
       <c r="K20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -1864,45 +1867,45 @@
         <v>11.11</v>
       </c>
       <c r="K21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -1917,45 +1920,45 @@
         <v>11.11</v>
       </c>
       <c r="K22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -1970,45 +1973,45 @@
         <v>11.11</v>
       </c>
       <c r="K23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -2023,45 +2026,45 @@
         <v>11.11</v>
       </c>
       <c r="K24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -2076,45 +2079,45 @@
         <v>11.11</v>
       </c>
       <c r="K25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -2129,45 +2132,45 @@
         <v>11.11</v>
       </c>
       <c r="K26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -2182,45 +2185,45 @@
         <v>11.11</v>
       </c>
       <c r="K27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -2235,45 +2238,45 @@
         <v>11.11</v>
       </c>
       <c r="K28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -2288,45 +2291,45 @@
         <v>11.11</v>
       </c>
       <c r="K29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E30">
         <v>3</v>
@@ -2341,45 +2344,45 @@
         <v>11.11</v>
       </c>
       <c r="K30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -2394,45 +2397,45 @@
         <v>11.11</v>
       </c>
       <c r="K31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -2447,45 +2450,45 @@
         <v>22.22</v>
       </c>
       <c r="K32" t="s">
+        <v>108</v>
+      </c>
+      <c r="L32" t="s">
+        <v>108</v>
+      </c>
+      <c r="M32" t="s">
+        <v>113</v>
+      </c>
+      <c r="N32" t="s">
+        <v>108</v>
+      </c>
+      <c r="O32" t="s">
         <v>109</v>
       </c>
-      <c r="L32" t="s">
-        <v>109</v>
-      </c>
-      <c r="M32" t="s">
-        <v>114</v>
-      </c>
-      <c r="N32" t="s">
-        <v>109</v>
-      </c>
-      <c r="O32" t="s">
-        <v>110</v>
-      </c>
       <c r="P32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -2500,45 +2503,45 @@
         <v>22.22</v>
       </c>
       <c r="K33" t="s">
+        <v>108</v>
+      </c>
+      <c r="L33" t="s">
+        <v>108</v>
+      </c>
+      <c r="M33" t="s">
+        <v>113</v>
+      </c>
+      <c r="N33" t="s">
+        <v>108</v>
+      </c>
+      <c r="O33" t="s">
         <v>109</v>
       </c>
-      <c r="L33" t="s">
-        <v>109</v>
-      </c>
-      <c r="M33" t="s">
-        <v>114</v>
-      </c>
-      <c r="N33" t="s">
-        <v>109</v>
-      </c>
-      <c r="O33" t="s">
-        <v>110</v>
-      </c>
       <c r="P33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -2553,45 +2556,45 @@
         <v>22.22</v>
       </c>
       <c r="K34" t="s">
+        <v>108</v>
+      </c>
+      <c r="L34" t="s">
+        <v>108</v>
+      </c>
+      <c r="M34" t="s">
+        <v>114</v>
+      </c>
+      <c r="N34" t="s">
+        <v>108</v>
+      </c>
+      <c r="O34" t="s">
         <v>109</v>
       </c>
-      <c r="L34" t="s">
-        <v>109</v>
-      </c>
-      <c r="M34" t="s">
-        <v>115</v>
-      </c>
-      <c r="N34" t="s">
-        <v>109</v>
-      </c>
-      <c r="O34" t="s">
-        <v>110</v>
-      </c>
       <c r="P34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -2606,45 +2609,45 @@
         <v>22.22</v>
       </c>
       <c r="K35" t="s">
+        <v>108</v>
+      </c>
+      <c r="L35" t="s">
+        <v>108</v>
+      </c>
+      <c r="M35" t="s">
+        <v>114</v>
+      </c>
+      <c r="N35" t="s">
+        <v>108</v>
+      </c>
+      <c r="O35" t="s">
         <v>109</v>
       </c>
-      <c r="L35" t="s">
-        <v>109</v>
-      </c>
-      <c r="M35" t="s">
-        <v>115</v>
-      </c>
-      <c r="N35" t="s">
-        <v>109</v>
-      </c>
-      <c r="O35" t="s">
-        <v>110</v>
-      </c>
       <c r="P35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E36">
         <v>3</v>
@@ -2659,45 +2662,45 @@
         <v>22.22</v>
       </c>
       <c r="K36" t="s">
+        <v>108</v>
+      </c>
+      <c r="L36" t="s">
+        <v>108</v>
+      </c>
+      <c r="M36" t="s">
+        <v>114</v>
+      </c>
+      <c r="N36" t="s">
+        <v>108</v>
+      </c>
+      <c r="O36" t="s">
         <v>109</v>
       </c>
-      <c r="L36" t="s">
-        <v>109</v>
-      </c>
-      <c r="M36" t="s">
-        <v>115</v>
-      </c>
-      <c r="N36" t="s">
-        <v>109</v>
-      </c>
-      <c r="O36" t="s">
-        <v>110</v>
-      </c>
       <c r="P36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -2712,45 +2715,45 @@
         <v>22.22</v>
       </c>
       <c r="K37" t="s">
+        <v>108</v>
+      </c>
+      <c r="L37" t="s">
+        <v>108</v>
+      </c>
+      <c r="M37" t="s">
+        <v>114</v>
+      </c>
+      <c r="N37" t="s">
+        <v>108</v>
+      </c>
+      <c r="O37" t="s">
         <v>109</v>
       </c>
-      <c r="L37" t="s">
-        <v>109</v>
-      </c>
-      <c r="M37" t="s">
-        <v>115</v>
-      </c>
-      <c r="N37" t="s">
-        <v>109</v>
-      </c>
-      <c r="O37" t="s">
-        <v>110</v>
-      </c>
       <c r="P37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -2765,45 +2768,45 @@
         <v>22.22</v>
       </c>
       <c r="K38" t="s">
+        <v>108</v>
+      </c>
+      <c r="L38" t="s">
+        <v>108</v>
+      </c>
+      <c r="M38" t="s">
+        <v>114</v>
+      </c>
+      <c r="N38" t="s">
+        <v>108</v>
+      </c>
+      <c r="O38" t="s">
         <v>109</v>
       </c>
-      <c r="L38" t="s">
-        <v>109</v>
-      </c>
-      <c r="M38" t="s">
-        <v>115</v>
-      </c>
-      <c r="N38" t="s">
-        <v>109</v>
-      </c>
-      <c r="O38" t="s">
-        <v>110</v>
-      </c>
       <c r="P38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E39">
         <v>3</v>
@@ -2818,45 +2821,45 @@
         <v>22.22</v>
       </c>
       <c r="K39" t="s">
+        <v>108</v>
+      </c>
+      <c r="L39" t="s">
+        <v>108</v>
+      </c>
+      <c r="M39" t="s">
+        <v>114</v>
+      </c>
+      <c r="N39" t="s">
+        <v>108</v>
+      </c>
+      <c r="O39" t="s">
         <v>109</v>
       </c>
-      <c r="L39" t="s">
-        <v>109</v>
-      </c>
-      <c r="M39" t="s">
-        <v>115</v>
-      </c>
-      <c r="N39" t="s">
-        <v>109</v>
-      </c>
-      <c r="O39" t="s">
-        <v>110</v>
-      </c>
       <c r="P39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -2871,45 +2874,45 @@
         <v>22.22</v>
       </c>
       <c r="K40" t="s">
+        <v>108</v>
+      </c>
+      <c r="L40" t="s">
+        <v>108</v>
+      </c>
+      <c r="M40" t="s">
+        <v>114</v>
+      </c>
+      <c r="N40" t="s">
+        <v>108</v>
+      </c>
+      <c r="O40" t="s">
         <v>109</v>
       </c>
-      <c r="L40" t="s">
-        <v>109</v>
-      </c>
-      <c r="M40" t="s">
-        <v>115</v>
-      </c>
-      <c r="N40" t="s">
-        <v>109</v>
-      </c>
-      <c r="O40" t="s">
-        <v>110</v>
-      </c>
       <c r="P40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -2924,45 +2927,45 @@
         <v>22.22</v>
       </c>
       <c r="K41" t="s">
+        <v>108</v>
+      </c>
+      <c r="L41" t="s">
+        <v>108</v>
+      </c>
+      <c r="M41" t="s">
+        <v>114</v>
+      </c>
+      <c r="N41" t="s">
+        <v>108</v>
+      </c>
+      <c r="O41" t="s">
         <v>109</v>
       </c>
-      <c r="L41" t="s">
-        <v>109</v>
-      </c>
-      <c r="M41" t="s">
-        <v>115</v>
-      </c>
-      <c r="N41" t="s">
-        <v>109</v>
-      </c>
-      <c r="O41" t="s">
-        <v>110</v>
-      </c>
       <c r="P41" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q41" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R41" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S41" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -2977,45 +2980,45 @@
         <v>22.22</v>
       </c>
       <c r="K42" t="s">
+        <v>108</v>
+      </c>
+      <c r="L42" t="s">
+        <v>108</v>
+      </c>
+      <c r="M42" t="s">
+        <v>114</v>
+      </c>
+      <c r="N42" t="s">
+        <v>108</v>
+      </c>
+      <c r="O42" t="s">
         <v>109</v>
       </c>
-      <c r="L42" t="s">
-        <v>109</v>
-      </c>
-      <c r="M42" t="s">
-        <v>115</v>
-      </c>
-      <c r="N42" t="s">
-        <v>109</v>
-      </c>
-      <c r="O42" t="s">
-        <v>110</v>
-      </c>
       <c r="P42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D43" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E43">
         <v>3</v>
@@ -3030,45 +3033,45 @@
         <v>22.22</v>
       </c>
       <c r="K43" t="s">
+        <v>108</v>
+      </c>
+      <c r="L43" t="s">
+        <v>108</v>
+      </c>
+      <c r="M43" t="s">
+        <v>114</v>
+      </c>
+      <c r="N43" t="s">
+        <v>108</v>
+      </c>
+      <c r="O43" t="s">
         <v>109</v>
       </c>
-      <c r="L43" t="s">
-        <v>109</v>
-      </c>
-      <c r="M43" t="s">
-        <v>115</v>
-      </c>
-      <c r="N43" t="s">
-        <v>109</v>
-      </c>
-      <c r="O43" t="s">
-        <v>110</v>
-      </c>
       <c r="P43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -3083,45 +3086,45 @@
         <v>22.22</v>
       </c>
       <c r="K44" t="s">
+        <v>108</v>
+      </c>
+      <c r="L44" t="s">
+        <v>108</v>
+      </c>
+      <c r="M44" t="s">
+        <v>115</v>
+      </c>
+      <c r="N44" t="s">
+        <v>108</v>
+      </c>
+      <c r="O44" t="s">
         <v>109</v>
       </c>
-      <c r="L44" t="s">
-        <v>109</v>
-      </c>
-      <c r="M44" t="s">
-        <v>116</v>
-      </c>
-      <c r="N44" t="s">
-        <v>109</v>
-      </c>
-      <c r="O44" t="s">
-        <v>110</v>
-      </c>
       <c r="P44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D45" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -3136,45 +3139,45 @@
         <v>22.22</v>
       </c>
       <c r="K45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M45" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E46">
         <v>4</v>
@@ -3189,45 +3192,45 @@
         <v>22.22</v>
       </c>
       <c r="K46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M46" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O46" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C47" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -3242,45 +3245,45 @@
         <v>22.22</v>
       </c>
       <c r="K47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E48">
         <v>3</v>
@@ -3295,45 +3298,45 @@
         <v>22.22</v>
       </c>
       <c r="K48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M48" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E49">
         <v>3</v>
@@ -3348,45 +3351,45 @@
         <v>22.22</v>
       </c>
       <c r="K49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M49" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O49" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -3401,45 +3404,45 @@
         <v>22.22</v>
       </c>
       <c r="K50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C51" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D51" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -3454,45 +3457,45 @@
         <v>22.22</v>
       </c>
       <c r="K51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M51" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C52" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3507,45 +3510,45 @@
         <v>22.22</v>
       </c>
       <c r="K52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M52" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O52" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C53" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -3560,45 +3563,45 @@
         <v>22.22</v>
       </c>
       <c r="K53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O53" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C54" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D54" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -3613,45 +3616,45 @@
         <v>22.22</v>
       </c>
       <c r="K54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O54" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D55" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -3666,45 +3669,45 @@
         <v>22.22</v>
       </c>
       <c r="K55" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L55" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M55" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N55" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O55" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P55" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q55" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R55" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S55" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E56">
         <v>3</v>
@@ -3719,45 +3722,45 @@
         <v>22.22</v>
       </c>
       <c r="K56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O56" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C57" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E57">
         <v>3</v>
@@ -3772,45 +3775,45 @@
         <v>22.22</v>
       </c>
       <c r="K57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O57" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E58">
         <v>3</v>
@@ -3825,45 +3828,45 @@
         <v>22.22</v>
       </c>
       <c r="K58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M58" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O58" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D59" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E59">
         <v>3</v>
@@ -3878,45 +3881,45 @@
         <v>22.22</v>
       </c>
       <c r="K59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M59" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O59" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E60">
         <v>4</v>
@@ -3931,45 +3934,45 @@
         <v>22.22</v>
       </c>
       <c r="K60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M60" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O60" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D61" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -3984,45 +3987,45 @@
         <v>22.22</v>
       </c>
       <c r="K61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M61" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O61" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C62" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D62" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4037,45 +4040,45 @@
         <v>22.22</v>
       </c>
       <c r="K62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O62" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C63" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D63" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E63">
         <v>3</v>
@@ -4090,45 +4093,45 @@
         <v>22.22</v>
       </c>
       <c r="K63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M63" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O63" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C64" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D64" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -4143,45 +4146,45 @@
         <v>22.22</v>
       </c>
       <c r="K64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M64" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O64" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -4196,45 +4199,45 @@
         <v>22.22</v>
       </c>
       <c r="K65" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L65" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M65" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N65" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O65" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P65" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q65" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R65" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S65" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C66" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D66" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E66">
         <v>3</v>
@@ -4249,45 +4252,45 @@
         <v>22.22</v>
       </c>
       <c r="K66" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L66" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M66" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N66" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O66" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P66" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q66" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R66" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S66" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C67" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D67" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E67">
         <v>3</v>
@@ -4302,45 +4305,45 @@
         <v>22.22</v>
       </c>
       <c r="K67" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L67" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M67" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N67" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O67" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P67" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q67" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R67" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S67" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D68" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E68">
         <v>3</v>
@@ -4355,45 +4358,45 @@
         <v>22.22</v>
       </c>
       <c r="K68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O68" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C69" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D69" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E69">
         <v>3</v>
@@ -4408,45 +4411,45 @@
         <v>33.33</v>
       </c>
       <c r="K69" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M69" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O69" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D70" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E70">
         <v>3</v>
@@ -4461,45 +4464,45 @@
         <v>33.33</v>
       </c>
       <c r="K70" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L70" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M70" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N70" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O70" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P70" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q70" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R70" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S70" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B71" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -4514,45 +4517,45 @@
         <v>33.33</v>
       </c>
       <c r="K71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M71" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O71" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B72" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C72" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E72">
         <v>3</v>
@@ -4567,45 +4570,45 @@
         <v>33.33</v>
       </c>
       <c r="K72" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L72" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M72" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N72" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O72" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P72" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q72" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R72" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S72" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C73" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D73" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E73">
         <v>4</v>
@@ -4620,45 +4623,45 @@
         <v>33.33</v>
       </c>
       <c r="K73" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L73" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M73" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N73" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O73" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P73" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q73" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R73" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S73" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C74" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D74" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E74">
         <v>3</v>
@@ -4673,45 +4676,45 @@
         <v>33.33</v>
       </c>
       <c r="K74" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L74" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M74" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N74" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O74" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P74" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q74" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R74" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S74" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E75">
         <v>3</v>
@@ -4726,45 +4729,45 @@
         <v>33.33</v>
       </c>
       <c r="K75" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L75" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M75" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N75" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O75" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P75" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q75" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R75" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S75" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C76" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E76">
         <v>3</v>
@@ -4779,45 +4782,45 @@
         <v>33.33</v>
       </c>
       <c r="K76" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M76" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O76" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C77" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D77" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E77">
         <v>3</v>
@@ -4832,45 +4835,45 @@
         <v>33.33</v>
       </c>
       <c r="K77" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M77" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O77" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D78" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E78">
         <v>3</v>
@@ -4885,45 +4888,45 @@
         <v>33.33</v>
       </c>
       <c r="K78" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L78" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M78" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N78" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P78" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q78" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R78" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S78" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C79" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E79">
         <v>3</v>
@@ -4938,45 +4941,45 @@
         <v>33.33</v>
       </c>
       <c r="K79" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L79" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M79" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N79" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P79" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q79" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R79" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S79" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B80" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C80" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D80" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E80">
         <v>3</v>
@@ -4991,45 +4994,45 @@
         <v>33.33</v>
       </c>
       <c r="K80" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L80" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M80" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N80" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O80" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P80" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q80" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R80" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S80" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B81" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C81" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D81" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E81">
         <v>3</v>
@@ -5044,45 +5047,45 @@
         <v>33.33</v>
       </c>
       <c r="K81" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L81" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M81" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N81" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O81" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P81" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q81" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R81" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S81" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D82" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E82">
         <v>4</v>
@@ -5097,45 +5100,45 @@
         <v>33.33</v>
       </c>
       <c r="K82" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L82" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M82" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N82" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O82" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P82" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q82" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R82" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S82" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C83" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D83" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E83">
         <v>4</v>
@@ -5150,45 +5153,45 @@
         <v>33.33</v>
       </c>
       <c r="K83" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L83" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M83" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N83" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O83" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P83" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q83" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R83" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S83" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C84" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D84" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E84">
         <v>3</v>
@@ -5203,45 +5206,45 @@
         <v>33.33</v>
       </c>
       <c r="K84" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L84" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M84" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N84" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O84" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P84" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q84" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R84" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S84" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D85" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E85">
         <v>3</v>
@@ -5256,45 +5259,45 @@
         <v>33.33</v>
       </c>
       <c r="K85" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L85" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M85" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N85" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O85" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P85" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q85" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R85" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S85" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B86" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C86" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D86" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5309,31 +5312,31 @@
         <v>33.33</v>
       </c>
       <c r="K86" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L86" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M86" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N86" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O86" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P86" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q86" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R86" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S86" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
